--- a/2. Báo cáo - giấy tờ/1. Báo cáo/Bàn giao/Bàn giao linh kiẹn Makipos-495.xlsx
+++ b/2. Báo cáo - giấy tờ/1. Báo cáo/Bàn giao/Bàn giao linh kiẹn Makipos-495.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TungNM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\1. Báo cáo\Bàn giao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D3E8EA-B85B-4160-8C49-88D232660246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C8660D-8CDF-4AB1-8A96-D037E46E957F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,6 +793,39 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,39 +843,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1270,72 +1270,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="23" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
     </row>
     <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="23" t="s">
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="23" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6" spans="1:5" ht="2.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="21" t="s">
         <v>140</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="22" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="21" t="s">
         <v>143</v>
       </c>
       <c r="B8" s="17"/>
@@ -1344,7 +1344,7 @@
       <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="21" t="s">
         <v>145</v>
       </c>
       <c r="B9" s="17"/>
@@ -1389,7 +1389,7 @@
       <c r="D12" s="13">
         <v>489</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="28" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       <c r="D13" s="13">
         <v>488</v>
       </c>
-      <c r="E13" s="34"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
@@ -1421,7 +1421,7 @@
       <c r="D14" s="13">
         <v>3465</v>
       </c>
-      <c r="E14" s="34"/>
+      <c r="E14" s="29"/>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
@@ -1436,7 +1436,7 @@
       <c r="D15" s="13">
         <v>990</v>
       </c>
-      <c r="E15" s="34"/>
+      <c r="E15" s="29"/>
     </row>
     <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
@@ -1451,7 +1451,7 @@
       <c r="D16" s="13">
         <v>990</v>
       </c>
-      <c r="E16" s="34"/>
+      <c r="E16" s="29"/>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
@@ -1466,7 +1466,7 @@
       <c r="D17" s="13">
         <v>2475</v>
       </c>
-      <c r="E17" s="34"/>
+      <c r="E17" s="29"/>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
@@ -1481,7 +1481,7 @@
       <c r="D18" s="13">
         <v>5445</v>
       </c>
-      <c r="E18" s="34"/>
+      <c r="E18" s="29"/>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
@@ -1496,7 +1496,7 @@
       <c r="D19" s="13">
         <v>990</v>
       </c>
-      <c r="E19" s="34"/>
+      <c r="E19" s="29"/>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
@@ -1511,7 +1511,7 @@
       <c r="D20" s="13">
         <v>495</v>
       </c>
-      <c r="E20" s="34"/>
+      <c r="E20" s="29"/>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
@@ -1526,7 +1526,7 @@
       <c r="D21" s="13">
         <v>40570</v>
       </c>
-      <c r="E21" s="34"/>
+      <c r="E21" s="29"/>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
@@ -1541,7 +1541,7 @@
       <c r="D22" s="13">
         <v>990</v>
       </c>
-      <c r="E22" s="34"/>
+      <c r="E22" s="29"/>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
@@ -1556,7 +1556,7 @@
       <c r="D23" s="13">
         <v>495</v>
       </c>
-      <c r="E23" s="34"/>
+      <c r="E23" s="29"/>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
@@ -1571,7 +1571,7 @@
       <c r="D24" s="13">
         <v>495</v>
       </c>
-      <c r="E24" s="34"/>
+      <c r="E24" s="29"/>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
@@ -1586,7 +1586,7 @@
       <c r="D25" s="13">
         <v>495</v>
       </c>
-      <c r="E25" s="34"/>
+      <c r="E25" s="29"/>
     </row>
     <row r="26" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
@@ -1601,7 +1601,7 @@
       <c r="D26" s="13">
         <v>495</v>
       </c>
-      <c r="E26" s="34"/>
+      <c r="E26" s="29"/>
     </row>
     <row r="27" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
@@ -1616,7 +1616,7 @@
       <c r="D27" s="13">
         <v>495</v>
       </c>
-      <c r="E27" s="34"/>
+      <c r="E27" s="29"/>
     </row>
     <row r="28" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
@@ -1631,7 +1631,7 @@
       <c r="D28" s="13">
         <v>495</v>
       </c>
-      <c r="E28" s="34"/>
+      <c r="E28" s="29"/>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
@@ -1646,7 +1646,7 @@
       <c r="D29" s="13">
         <v>3945</v>
       </c>
-      <c r="E29" s="34"/>
+      <c r="E29" s="29"/>
     </row>
     <row r="30" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
@@ -1661,7 +1661,7 @@
       <c r="D30" s="13">
         <v>13360</v>
       </c>
-      <c r="E30" s="34"/>
+      <c r="E30" s="29"/>
     </row>
     <row r="31" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
@@ -1676,7 +1676,7 @@
       <c r="D31" s="13">
         <v>1485</v>
       </c>
-      <c r="E31" s="34"/>
+      <c r="E31" s="29"/>
     </row>
     <row r="32" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
@@ -1691,7 +1691,7 @@
       <c r="D32" s="13">
         <v>3960</v>
       </c>
-      <c r="E32" s="34"/>
+      <c r="E32" s="29"/>
     </row>
     <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
@@ -1706,7 +1706,7 @@
       <c r="D33" s="13">
         <v>495</v>
       </c>
-      <c r="E33" s="34"/>
+      <c r="E33" s="29"/>
     </row>
     <row r="34" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
@@ -1721,7 +1721,7 @@
       <c r="D34" s="13">
         <v>495</v>
       </c>
-      <c r="E34" s="34"/>
+      <c r="E34" s="29"/>
     </row>
     <row r="35" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
@@ -1736,7 +1736,7 @@
       <c r="D35" s="13">
         <v>990</v>
       </c>
-      <c r="E35" s="34"/>
+      <c r="E35" s="29"/>
     </row>
     <row r="36" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
@@ -1751,7 +1751,7 @@
       <c r="D36" s="13">
         <v>495</v>
       </c>
-      <c r="E36" s="34"/>
+      <c r="E36" s="29"/>
     </row>
     <row r="37" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
@@ -1766,7 +1766,7 @@
       <c r="D37" s="13">
         <v>495</v>
       </c>
-      <c r="E37" s="34"/>
+      <c r="E37" s="29"/>
     </row>
     <row r="38" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
@@ -1781,7 +1781,7 @@
       <c r="D38" s="13">
         <v>495</v>
       </c>
-      <c r="E38" s="34"/>
+      <c r="E38" s="29"/>
     </row>
     <row r="39" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
@@ -1796,7 +1796,7 @@
       <c r="D39" s="13">
         <v>990</v>
       </c>
-      <c r="E39" s="34"/>
+      <c r="E39" s="29"/>
     </row>
     <row r="40" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
@@ -1811,7 +1811,7 @@
       <c r="D40" s="13">
         <v>990</v>
       </c>
-      <c r="E40" s="34"/>
+      <c r="E40" s="29"/>
     </row>
     <row r="41" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
@@ -1826,7 +1826,7 @@
       <c r="D41" s="13">
         <v>495</v>
       </c>
-      <c r="E41" s="34"/>
+      <c r="E41" s="29"/>
     </row>
     <row r="42" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
@@ -1841,7 +1841,7 @@
       <c r="D42" s="13">
         <v>495</v>
       </c>
-      <c r="E42" s="34"/>
+      <c r="E42" s="29"/>
     </row>
     <row r="43" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
@@ -1856,7 +1856,7 @@
       <c r="D43" s="13">
         <v>495</v>
       </c>
-      <c r="E43" s="34"/>
+      <c r="E43" s="29"/>
     </row>
     <row r="44" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
@@ -1871,7 +1871,7 @@
       <c r="D44" s="13">
         <v>985</v>
       </c>
-      <c r="E44" s="34"/>
+      <c r="E44" s="29"/>
     </row>
     <row r="45" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
@@ -1886,7 +1886,7 @@
       <c r="D45" s="13">
         <v>495</v>
       </c>
-      <c r="E45" s="34"/>
+      <c r="E45" s="29"/>
     </row>
     <row r="46" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
@@ -1901,7 +1901,7 @@
       <c r="D46" s="13">
         <v>495</v>
       </c>
-      <c r="E46" s="34"/>
+      <c r="E46" s="29"/>
     </row>
     <row r="47" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
@@ -1916,7 +1916,7 @@
       <c r="D47" s="13">
         <v>500</v>
       </c>
-      <c r="E47" s="34"/>
+      <c r="E47" s="29"/>
     </row>
     <row r="48" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
@@ -1931,7 +1931,7 @@
       <c r="D48" s="13">
         <v>495</v>
       </c>
-      <c r="E48" s="34"/>
+      <c r="E48" s="29"/>
     </row>
     <row r="49" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
@@ -1946,7 +1946,7 @@
       <c r="D49" s="13">
         <v>495</v>
       </c>
-      <c r="E49" s="34"/>
+      <c r="E49" s="29"/>
     </row>
     <row r="50" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
@@ -1961,7 +1961,7 @@
       <c r="D50" s="13">
         <v>4445</v>
       </c>
-      <c r="E50" s="34"/>
+      <c r="E50" s="29"/>
     </row>
     <row r="51" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
@@ -1976,7 +1976,7 @@
       <c r="D51" s="13">
         <v>2970</v>
       </c>
-      <c r="E51" s="34"/>
+      <c r="E51" s="29"/>
     </row>
     <row r="52" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
@@ -1991,7 +1991,7 @@
       <c r="D52" s="13">
         <v>495</v>
       </c>
-      <c r="E52" s="34"/>
+      <c r="E52" s="29"/>
     </row>
     <row r="53" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
@@ -2006,7 +2006,7 @@
       <c r="D53" s="13">
         <v>495</v>
       </c>
-      <c r="E53" s="34"/>
+      <c r="E53" s="29"/>
     </row>
     <row r="54" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
@@ -2021,7 +2021,7 @@
       <c r="D54" s="13">
         <v>490</v>
       </c>
-      <c r="E54" s="34"/>
+      <c r="E54" s="29"/>
     </row>
     <row r="55" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
@@ -2036,7 +2036,7 @@
       <c r="D55" s="13">
         <v>6915</v>
       </c>
-      <c r="E55" s="34"/>
+      <c r="E55" s="29"/>
     </row>
     <row r="56" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
@@ -2051,7 +2051,7 @@
       <c r="D56" s="13">
         <v>495</v>
       </c>
-      <c r="E56" s="34"/>
+      <c r="E56" s="29"/>
     </row>
     <row r="57" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
@@ -2066,7 +2066,7 @@
       <c r="D57" s="13">
         <v>2475</v>
       </c>
-      <c r="E57" s="34"/>
+      <c r="E57" s="29"/>
     </row>
     <row r="58" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
@@ -2081,7 +2081,7 @@
       <c r="D58" s="13">
         <v>990</v>
       </c>
-      <c r="E58" s="34"/>
+      <c r="E58" s="29"/>
     </row>
     <row r="59" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
@@ -2096,7 +2096,7 @@
       <c r="D59" s="13">
         <v>495</v>
       </c>
-      <c r="E59" s="34"/>
+      <c r="E59" s="29"/>
     </row>
     <row r="60" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
@@ -2111,7 +2111,7 @@
       <c r="D60" s="13">
         <v>495</v>
       </c>
-      <c r="E60" s="34"/>
+      <c r="E60" s="29"/>
     </row>
     <row r="61" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
@@ -2126,7 +2126,7 @@
       <c r="D61" s="13">
         <v>990</v>
       </c>
-      <c r="E61" s="34"/>
+      <c r="E61" s="29"/>
     </row>
     <row r="62" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
@@ -2141,7 +2141,7 @@
       <c r="D62" s="13">
         <v>4950</v>
       </c>
-      <c r="E62" s="34"/>
+      <c r="E62" s="29"/>
     </row>
     <row r="63" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
@@ -2156,7 +2156,7 @@
       <c r="D63" s="13">
         <v>2970</v>
       </c>
-      <c r="E63" s="34"/>
+      <c r="E63" s="29"/>
     </row>
     <row r="64" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
@@ -2171,7 +2171,7 @@
       <c r="D64" s="13">
         <v>6435</v>
       </c>
-      <c r="E64" s="34"/>
+      <c r="E64" s="29"/>
     </row>
     <row r="65" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
@@ -2186,7 +2186,7 @@
       <c r="D65" s="13">
         <v>990</v>
       </c>
-      <c r="E65" s="34"/>
+      <c r="E65" s="29"/>
     </row>
     <row r="66" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
@@ -2201,7 +2201,7 @@
       <c r="D66" s="13">
         <v>495</v>
       </c>
-      <c r="E66" s="34"/>
+      <c r="E66" s="29"/>
     </row>
     <row r="67" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
@@ -2216,7 +2216,7 @@
       <c r="D67" s="13">
         <v>990</v>
       </c>
-      <c r="E67" s="34"/>
+      <c r="E67" s="29"/>
     </row>
     <row r="68" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
@@ -2231,7 +2231,7 @@
       <c r="D68" s="13">
         <v>495</v>
       </c>
-      <c r="E68" s="34"/>
+      <c r="E68" s="29"/>
     </row>
     <row r="69" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
@@ -2246,7 +2246,7 @@
       <c r="D69" s="13">
         <v>495</v>
       </c>
-      <c r="E69" s="34"/>
+      <c r="E69" s="29"/>
     </row>
     <row r="70" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
@@ -2261,7 +2261,7 @@
       <c r="D70" s="13">
         <v>1980</v>
       </c>
-      <c r="E70" s="34"/>
+      <c r="E70" s="29"/>
     </row>
     <row r="71" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
@@ -2276,7 +2276,7 @@
       <c r="D71" s="13">
         <v>1485</v>
       </c>
-      <c r="E71" s="34"/>
+      <c r="E71" s="29"/>
     </row>
     <row r="72" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
@@ -2291,7 +2291,7 @@
       <c r="D72" s="13">
         <v>990</v>
       </c>
-      <c r="E72" s="34"/>
+      <c r="E72" s="29"/>
     </row>
     <row r="73" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
@@ -2306,7 +2306,7 @@
       <c r="D73" s="13">
         <v>495</v>
       </c>
-      <c r="E73" s="34"/>
+      <c r="E73" s="29"/>
     </row>
     <row r="74" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
@@ -2321,7 +2321,7 @@
       <c r="D74" s="13">
         <v>495</v>
       </c>
-      <c r="E74" s="34"/>
+      <c r="E74" s="29"/>
     </row>
     <row r="75" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
@@ -2336,7 +2336,7 @@
       <c r="D75" s="13">
         <v>495</v>
       </c>
-      <c r="E75" s="34"/>
+      <c r="E75" s="29"/>
     </row>
     <row r="76" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
@@ -2351,7 +2351,7 @@
       <c r="D76" s="13">
         <v>495</v>
       </c>
-      <c r="E76" s="34"/>
+      <c r="E76" s="29"/>
     </row>
     <row r="77" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
@@ -2366,7 +2366,7 @@
       <c r="D77" s="13">
         <v>495</v>
       </c>
-      <c r="E77" s="34"/>
+      <c r="E77" s="29"/>
     </row>
     <row r="78" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
@@ -2381,7 +2381,7 @@
       <c r="D78" s="13">
         <v>495</v>
       </c>
-      <c r="E78" s="34"/>
+      <c r="E78" s="29"/>
     </row>
     <row r="79" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
@@ -2396,7 +2396,7 @@
       <c r="D79" s="13">
         <v>495</v>
       </c>
-      <c r="E79" s="34"/>
+      <c r="E79" s="29"/>
     </row>
     <row r="80" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
@@ -2411,7 +2411,7 @@
       <c r="D80" s="13">
         <v>495</v>
       </c>
-      <c r="E80" s="34"/>
+      <c r="E80" s="29"/>
     </row>
     <row r="81" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
@@ -2426,7 +2426,7 @@
       <c r="D81" s="13">
         <v>990</v>
       </c>
-      <c r="E81" s="34"/>
+      <c r="E81" s="29"/>
     </row>
     <row r="82" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
@@ -2441,7 +2441,7 @@
       <c r="D82" s="13">
         <v>495</v>
       </c>
-      <c r="E82" s="34"/>
+      <c r="E82" s="29"/>
     </row>
     <row r="83" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
@@ -2456,7 +2456,7 @@
       <c r="D83" s="13">
         <v>495</v>
       </c>
-      <c r="E83" s="34"/>
+      <c r="E83" s="29"/>
     </row>
     <row r="84" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
@@ -2471,7 +2471,7 @@
       <c r="D84" s="13">
         <v>1480</v>
       </c>
-      <c r="E84" s="34"/>
+      <c r="E84" s="29"/>
     </row>
     <row r="85" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
@@ -2486,7 +2486,7 @@
       <c r="D85" s="13">
         <v>1485</v>
       </c>
-      <c r="E85" s="34"/>
+      <c r="E85" s="29"/>
     </row>
     <row r="86" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
@@ -2501,7 +2501,7 @@
       <c r="D86" s="13">
         <v>495</v>
       </c>
-      <c r="E86" s="34"/>
+      <c r="E86" s="29"/>
     </row>
     <row r="87" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
@@ -2516,7 +2516,7 @@
       <c r="D87" s="13">
         <v>3455</v>
       </c>
-      <c r="E87" s="34"/>
+      <c r="E87" s="29"/>
     </row>
     <row r="88" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
@@ -2531,7 +2531,7 @@
       <c r="D88" s="13">
         <v>495</v>
       </c>
-      <c r="E88" s="34"/>
+      <c r="E88" s="29"/>
     </row>
     <row r="89" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
@@ -2546,7 +2546,7 @@
       <c r="D89" s="13">
         <v>2970</v>
       </c>
-      <c r="E89" s="34"/>
+      <c r="E89" s="29"/>
     </row>
     <row r="90" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
@@ -2561,7 +2561,7 @@
       <c r="D90" s="13">
         <v>495</v>
       </c>
-      <c r="E90" s="34"/>
+      <c r="E90" s="29"/>
     </row>
     <row r="91" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
@@ -2576,7 +2576,7 @@
       <c r="D91" s="13">
         <v>495</v>
       </c>
-      <c r="E91" s="34"/>
+      <c r="E91" s="29"/>
     </row>
     <row r="92" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
@@ -2591,7 +2591,7 @@
       <c r="D92" s="13">
         <v>4950</v>
       </c>
-      <c r="E92" s="34"/>
+      <c r="E92" s="29"/>
     </row>
     <row r="93" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
@@ -2606,7 +2606,7 @@
       <c r="D93" s="13">
         <v>495</v>
       </c>
-      <c r="E93" s="34"/>
+      <c r="E93" s="29"/>
     </row>
     <row r="94" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
@@ -2621,7 +2621,7 @@
       <c r="D94" s="13">
         <v>495</v>
       </c>
-      <c r="E94" s="34"/>
+      <c r="E94" s="29"/>
     </row>
     <row r="95" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
@@ -2636,7 +2636,7 @@
       <c r="D95" s="13">
         <v>21090</v>
       </c>
-      <c r="E95" s="34"/>
+      <c r="E95" s="29"/>
     </row>
     <row r="96" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
@@ -2651,7 +2651,7 @@
       <c r="D96" s="13">
         <v>16805</v>
       </c>
-      <c r="E96" s="34"/>
+      <c r="E96" s="29"/>
     </row>
     <row r="97" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
@@ -2666,7 +2666,7 @@
       <c r="D97" s="13">
         <v>495</v>
       </c>
-      <c r="E97" s="34"/>
+      <c r="E97" s="29"/>
     </row>
     <row r="98" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
@@ -2681,7 +2681,7 @@
       <c r="D98" s="13">
         <v>495</v>
       </c>
-      <c r="E98" s="34"/>
+      <c r="E98" s="29"/>
     </row>
     <row r="99" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
@@ -2696,7 +2696,7 @@
       <c r="D99" s="13">
         <v>990</v>
       </c>
-      <c r="E99" s="34"/>
+      <c r="E99" s="29"/>
     </row>
     <row r="100" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
@@ -2711,7 +2711,7 @@
       <c r="D100" s="13">
         <v>495</v>
       </c>
-      <c r="E100" s="34"/>
+      <c r="E100" s="29"/>
     </row>
     <row r="101" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
@@ -2726,7 +2726,7 @@
       <c r="D101" s="13">
         <v>500</v>
       </c>
-      <c r="E101" s="34"/>
+      <c r="E101" s="29"/>
     </row>
     <row r="102" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
@@ -2741,7 +2741,7 @@
       <c r="D102" s="13">
         <v>495</v>
       </c>
-      <c r="E102" s="34"/>
+      <c r="E102" s="29"/>
     </row>
     <row r="103" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
@@ -2756,7 +2756,7 @@
       <c r="D103" s="13">
         <v>2475</v>
       </c>
-      <c r="E103" s="34"/>
+      <c r="E103" s="29"/>
     </row>
     <row r="104" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
@@ -2771,7 +2771,7 @@
       <c r="D104" s="13">
         <v>9385</v>
       </c>
-      <c r="E104" s="34"/>
+      <c r="E104" s="29"/>
     </row>
     <row r="105" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
@@ -2786,7 +2786,7 @@
       <c r="D105" s="13">
         <v>495</v>
       </c>
-      <c r="E105" s="34"/>
+      <c r="E105" s="29"/>
     </row>
     <row r="106" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
@@ -2801,7 +2801,7 @@
       <c r="D106" s="13">
         <v>495</v>
       </c>
-      <c r="E106" s="34"/>
+      <c r="E106" s="29"/>
     </row>
     <row r="107" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
@@ -2816,7 +2816,7 @@
       <c r="D107" s="13">
         <v>495</v>
       </c>
-      <c r="E107" s="34"/>
+      <c r="E107" s="29"/>
     </row>
     <row r="108" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
@@ -2831,7 +2831,7 @@
       <c r="D108" s="13">
         <v>495</v>
       </c>
-      <c r="E108" s="34"/>
+      <c r="E108" s="29"/>
     </row>
     <row r="109" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
@@ -2846,7 +2846,7 @@
       <c r="D109" s="13">
         <v>7400</v>
       </c>
-      <c r="E109" s="34"/>
+      <c r="E109" s="29"/>
     </row>
     <row r="110" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
@@ -2861,7 +2861,7 @@
       <c r="D110" s="13">
         <v>990</v>
       </c>
-      <c r="E110" s="34"/>
+      <c r="E110" s="29"/>
     </row>
     <row r="111" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
@@ -2876,7 +2876,7 @@
       <c r="D111" s="13">
         <v>13365</v>
       </c>
-      <c r="E111" s="34"/>
+      <c r="E111" s="29"/>
     </row>
     <row r="112" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
@@ -2891,7 +2891,7 @@
       <c r="D112" s="13">
         <v>495</v>
       </c>
-      <c r="E112" s="34"/>
+      <c r="E112" s="29"/>
     </row>
     <row r="113" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
@@ -2906,7 +2906,7 @@
       <c r="D113" s="13">
         <v>990</v>
       </c>
-      <c r="E113" s="34"/>
+      <c r="E113" s="29"/>
     </row>
     <row r="114" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
@@ -2921,7 +2921,7 @@
       <c r="D114" s="13">
         <v>10000</v>
       </c>
-      <c r="E114" s="34"/>
+      <c r="E114" s="29"/>
     </row>
     <row r="115" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
@@ -2936,7 +2936,7 @@
       <c r="D115" s="13">
         <v>490</v>
       </c>
-      <c r="E115" s="34"/>
+      <c r="E115" s="29"/>
     </row>
     <row r="116" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
@@ -2951,7 +2951,7 @@
       <c r="D116" s="13">
         <v>495</v>
       </c>
-      <c r="E116" s="34"/>
+      <c r="E116" s="29"/>
     </row>
     <row r="117" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
@@ -2966,7 +2966,7 @@
       <c r="D117" s="13">
         <v>4450</v>
       </c>
-      <c r="E117" s="34"/>
+      <c r="E117" s="29"/>
     </row>
     <row r="118" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
@@ -2981,7 +2981,7 @@
       <c r="D118" s="13">
         <v>1980</v>
       </c>
-      <c r="E118" s="34"/>
+      <c r="E118" s="29"/>
     </row>
     <row r="119" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
@@ -2996,7 +2996,7 @@
       <c r="D119" s="13">
         <v>495</v>
       </c>
-      <c r="E119" s="34"/>
+      <c r="E119" s="29"/>
     </row>
     <row r="120" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
@@ -3011,7 +3011,7 @@
       <c r="D120" s="13">
         <v>8420</v>
       </c>
-      <c r="E120" s="34"/>
+      <c r="E120" s="29"/>
     </row>
     <row r="121" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
@@ -3026,7 +3026,7 @@
       <c r="D121" s="13">
         <v>495</v>
       </c>
-      <c r="E121" s="34"/>
+      <c r="E121" s="29"/>
     </row>
     <row r="122" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
@@ -3041,7 +3041,7 @@
       <c r="D122" s="13">
         <v>495</v>
       </c>
-      <c r="E122" s="34"/>
+      <c r="E122" s="29"/>
     </row>
     <row r="123" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
@@ -3056,7 +3056,7 @@
       <c r="D123" s="13">
         <v>495</v>
       </c>
-      <c r="E123" s="34"/>
+      <c r="E123" s="29"/>
     </row>
     <row r="124" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
@@ -3071,7 +3071,7 @@
       <c r="D124" s="13">
         <v>495</v>
       </c>
-      <c r="E124" s="34"/>
+      <c r="E124" s="29"/>
     </row>
     <row r="125" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
@@ -3086,7 +3086,7 @@
       <c r="D125" s="13">
         <v>495</v>
       </c>
-      <c r="E125" s="34"/>
+      <c r="E125" s="29"/>
     </row>
     <row r="126" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
@@ -3101,7 +3101,7 @@
       <c r="D126" s="13">
         <v>495</v>
       </c>
-      <c r="E126" s="34"/>
+      <c r="E126" s="29"/>
     </row>
     <row r="127" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
@@ -3116,7 +3116,7 @@
       <c r="D127" s="13">
         <v>495</v>
       </c>
-      <c r="E127" s="34"/>
+      <c r="E127" s="29"/>
     </row>
     <row r="128" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
@@ -3131,7 +3131,7 @@
       <c r="D128" s="13">
         <v>495</v>
       </c>
-      <c r="E128" s="34"/>
+      <c r="E128" s="29"/>
     </row>
     <row r="129" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
@@ -3146,7 +3146,7 @@
       <c r="D129" s="13">
         <v>495</v>
       </c>
-      <c r="E129" s="34"/>
+      <c r="E129" s="29"/>
     </row>
     <row r="130" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
@@ -3161,7 +3161,7 @@
       <c r="D130" s="13">
         <v>1325</v>
       </c>
-      <c r="E130" s="34"/>
+      <c r="E130" s="29"/>
     </row>
     <row r="131" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
@@ -3176,7 +3176,7 @@
       <c r="D131" s="13">
         <v>495</v>
       </c>
-      <c r="E131" s="34"/>
+      <c r="E131" s="29"/>
     </row>
     <row r="132" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
@@ -3191,7 +3191,7 @@
       <c r="D132" s="13">
         <v>495</v>
       </c>
-      <c r="E132" s="34"/>
+      <c r="E132" s="29"/>
     </row>
     <row r="133" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
@@ -3206,7 +3206,7 @@
       <c r="D133" s="13">
         <v>11380</v>
       </c>
-      <c r="E133" s="34"/>
+      <c r="E133" s="29"/>
     </row>
     <row r="134" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
@@ -3221,7 +3221,7 @@
       <c r="D134" s="13">
         <v>495</v>
       </c>
-      <c r="E134" s="34"/>
+      <c r="E134" s="29"/>
     </row>
     <row r="135" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
@@ -3236,7 +3236,7 @@
       <c r="D135" s="13">
         <v>495</v>
       </c>
-      <c r="E135" s="34"/>
+      <c r="E135" s="29"/>
     </row>
     <row r="136" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
@@ -3251,7 +3251,7 @@
       <c r="D136" s="13">
         <v>1485</v>
       </c>
-      <c r="E136" s="34"/>
+      <c r="E136" s="29"/>
     </row>
     <row r="137" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
@@ -3266,7 +3266,7 @@
       <c r="D137" s="13">
         <v>495</v>
       </c>
-      <c r="E137" s="34"/>
+      <c r="E137" s="29"/>
     </row>
     <row r="138" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
@@ -3281,13 +3281,13 @@
       <c r="D138" s="13">
         <v>990</v>
       </c>
-      <c r="E138" s="34"/>
+      <c r="E138" s="29"/>
     </row>
     <row r="139" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>128</v>
       </c>
-      <c r="B139" s="31" t="s">
+      <c r="B139" s="20" t="s">
         <v>130</v>
       </c>
       <c r="C139" s="12" t="s">
@@ -3296,7 +3296,7 @@
       <c r="D139" s="13">
         <v>495</v>
       </c>
-      <c r="E139" s="35"/>
+      <c r="E139" s="30"/>
     </row>
     <row r="140" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="5"/>
@@ -3313,26 +3313,26 @@
       <c r="E141" s="19"/>
     </row>
     <row r="142" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="29" t="s">
+      <c r="A142" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="B142" s="29"/>
+      <c r="B142" s="26"/>
       <c r="C142" s="7"/>
-      <c r="D142" s="29" t="s">
+      <c r="D142" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="E142" s="29"/>
+      <c r="E142" s="26"/>
     </row>
     <row r="143" spans="1:5" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="30" t="s">
+      <c r="A143" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B143" s="30"/>
+      <c r="B143" s="27"/>
       <c r="C143" s="9"/>
-      <c r="D143" s="30" t="s">
+      <c r="D143" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="E143" s="30"/>
+      <c r="E143" s="27"/>
     </row>
     <row r="144" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A144" s="7"/>
@@ -3370,11 +3370,11 @@
       <c r="E148" s="7"/>
     </row>
     <row r="149" spans="1:5" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
+      <c r="A149" s="26"/>
+      <c r="B149" s="26"/>
       <c r="C149" s="7"/>
-      <c r="D149" s="29"/>
-      <c r="E149" s="29"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
     </row>
     <row r="150" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="151" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3394,6 +3394,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A1:B4"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="D142:E142"/>
     <mergeCell ref="A142:B142"/>
@@ -3402,12 +3408,6 @@
     <mergeCell ref="D143:E143"/>
     <mergeCell ref="D149:E149"/>
     <mergeCell ref="E12:E139"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A1:B4"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
